--- a/artfynd/S 1272-2023 artfynd.xlsx
+++ b/artfynd/S 1272-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99746</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/153386</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120634226</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120634229</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88565042</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1432,6 +1467,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/387421</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/454248</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86636325</t>
         </is>
       </c>
     </row>
@@ -1764,6 +1814,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95345523</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120634228</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1970,6 +2030,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065371</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2067,6 +2132,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065372</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2169,6 +2239,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82850879</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2271,6 +2346,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82841886</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2373,6 +2453,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82836627</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2482,6 +2567,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065308</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2593,6 +2683,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76389000</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79261008</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115356870</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2938,6 +3043,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13647811</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3049,6 +3159,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104020290</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3180,6 +3295,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68810460</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3311,6 +3431,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68810483</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3432,6 +3557,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126603285</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3554,6 +3684,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68938507</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3679,6 +3814,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110477051</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3804,6 +3944,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110477043</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3929,6 +4074,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108714792</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4054,6 +4204,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108714716</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4179,6 +4334,11 @@
           <t>Mittlandets fåglar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110380923</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4302,6 +4462,11 @@
       <c r="AY33" t="inlineStr">
         <is>
           <t>Mittlandets fåglar</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108714784</t>
         </is>
       </c>
     </row>
@@ -4419,6 +4584,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115356931</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4541,6 +4711,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68938621</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4645,6 +4820,11 @@
       <c r="AY36" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2148727</t>
         </is>
       </c>
     </row>
@@ -4753,6 +4933,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82836541</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4862,6 +5047,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65298384</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4971,6 +5161,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65298394</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5077,6 +5272,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2909690</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5183,6 +5383,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2924779</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5284,6 +5489,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065350</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5385,6 +5595,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065369</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5498,6 +5713,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81544586</t>
         </is>
       </c>
     </row>
@@ -5611,6 +5831,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81544593</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5721,6 +5946,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85925189</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5831,6 +6061,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85925272</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5952,6 +6187,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67969782</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6058,6 +6298,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2597656</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6164,6 +6409,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2765034</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6270,6 +6520,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17316915</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6374,6 +6629,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79494784</t>
         </is>
       </c>
     </row>
@@ -6483,6 +6743,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95345533</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6589,6 +6854,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3435824</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6695,6 +6965,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3435826</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6801,6 +7076,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3367706</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6912,6 +7192,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3370548</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7018,6 +7303,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3916155</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7124,6 +7414,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3925939</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7230,6 +7525,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3927882</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7336,6 +7636,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66239940</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7435,6 +7740,11 @@
       <c r="AY62" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065246</t>
         </is>
       </c>
     </row>
@@ -7544,6 +7854,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95345550</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7650,6 +7965,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3919102</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7751,6 +8071,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065249</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7857,6 +8182,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4803939</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7969,6 +8299,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57895162</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8082,6 +8417,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64448356</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8183,6 +8523,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065260</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8284,6 +8629,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065261</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8400,6 +8750,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82139337</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8510,6 +8865,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115356913</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8616,6 +8976,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5022818</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8727,6 +9092,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5031633</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8837,6 +9207,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82836640</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8936,6 +9311,11 @@
       <c r="AY76" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065300</t>
         </is>
       </c>
     </row>
@@ -9044,6 +9424,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86655199</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9145,6 +9530,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065310</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9251,6 +9641,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81065333</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9353,6 +9748,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66239941</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9462,6 +9862,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120634271</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9567,8 +9972,96 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82852681</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>